--- a/Data/Cleaned/Pooled/wage_inequality_overall.xlsx
+++ b/Data/Cleaned/Pooled/wage_inequality_overall.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandeepsharma/Desktop/Research/Data Analysis/Formal Informal wage/Formal_informal_wage/Data/Cleaned/Pooled/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{FB92A8F7-65B6-7345-80D8-78F73CB9E850}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{FCB0EFD7-A317-9E40-9D9C-BFD1EF69D95A}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="27320" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2008" sheetId="1" r:id="rId1"/>
+    <sheet name="2018" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="30">
   <si>
     <t>t</t>
   </si>
@@ -151,11 +152,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2759,4 +2761,2297 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A73C87-4E98-8A47-9331-D303F239DB09}">
+  <dimension ref="A1:AE24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S1" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>1.80406E-2</v>
+      </c>
+      <c r="C2">
+        <v>7.8388999999999993E-3</v>
+      </c>
+      <c r="D2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E2">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.6738999999999999E-3</v>
+      </c>
+      <c r="G2">
+        <v>3.3407300000000001E-2</v>
+      </c>
+      <c r="H2">
+        <v>2.05854E-2</v>
+      </c>
+      <c r="I2">
+        <v>5.3543999999999996E-3</v>
+      </c>
+      <c r="J2">
+        <v>3.84</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1.00891E-2</v>
+      </c>
+      <c r="M2">
+        <v>3.1081600000000001E-2</v>
+      </c>
+      <c r="N2">
+        <v>2.3534800000000002E-2</v>
+      </c>
+      <c r="O2">
+        <v>3.9274999999999996E-3</v>
+      </c>
+      <c r="P2">
+        <v>5.99</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>1.5835700000000001E-2</v>
+      </c>
+      <c r="S2">
+        <v>3.1233899999999998E-2</v>
+      </c>
+      <c r="T2">
+        <v>3.3852E-2</v>
+      </c>
+      <c r="U2">
+        <v>3.4175999999999998E-3</v>
+      </c>
+      <c r="V2">
+        <v>9.91</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>2.71524E-2</v>
+      </c>
+      <c r="Y2">
+        <v>4.0551700000000003E-2</v>
+      </c>
+      <c r="Z2">
+        <v>2.3692899999999999E-2</v>
+      </c>
+      <c r="AA2">
+        <v>4.4600000000000004E-3</v>
+      </c>
+      <c r="AB2">
+        <v>5.31</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>1.495E-2</v>
+      </c>
+      <c r="AE2">
+        <v>3.2435800000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>-2.8019999999999998E-4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.6750000000000001E-4</v>
+      </c>
+      <c r="D3" s="2">
+        <v>-1.67</v>
+      </c>
+      <c r="E3" s="2">
+        <v>9.4E-2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>-6.0849999999999999E-4</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4.8000000000000001E-5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>-2.23E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1.064E-4</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-2.1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L3" s="2">
+        <v>-4.3159999999999997E-4</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-1.4399999999999999E-5</v>
+      </c>
+      <c r="N3" s="2">
+        <v>-2.6800000000000001E-4</v>
+      </c>
+      <c r="O3" s="2">
+        <v>7.7100000000000004E-5</v>
+      </c>
+      <c r="P3" s="2">
+        <v>-3.47</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="R3" s="2">
+        <v>-4.191E-4</v>
+      </c>
+      <c r="S3" s="2">
+        <v>-1.1680000000000001E-4</v>
+      </c>
+      <c r="T3" s="2">
+        <v>-4.7029999999999999E-4</v>
+      </c>
+      <c r="U3" s="2">
+        <v>5.9799999999999997E-5</v>
+      </c>
+      <c r="V3" s="2">
+        <v>-7.87</v>
+      </c>
+      <c r="W3" s="2">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2">
+        <v>-5.8750000000000002E-4</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>-3.5310000000000002E-4</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>-3.4749999999999999E-4</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>6.9900000000000005E-5</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>-4.97</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>-4.8460000000000002E-4</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>-2.1039999999999999E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>7.5680399999999995E-2</v>
+      </c>
+      <c r="C4">
+        <v>0.16345770000000001</v>
+      </c>
+      <c r="D4">
+        <v>0.46</v>
+      </c>
+      <c r="E4">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="F4">
+        <v>-0.24474850000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.39610919999999999</v>
+      </c>
+      <c r="H4">
+        <v>2.7637100000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>9.6596600000000005E-2</v>
+      </c>
+      <c r="J4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="K4">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="L4">
+        <v>-0.1617228</v>
+      </c>
+      <c r="M4">
+        <v>0.216997</v>
+      </c>
+      <c r="N4">
+        <v>0.1507433</v>
+      </c>
+      <c r="O4">
+        <v>6.3693200000000005E-2</v>
+      </c>
+      <c r="P4">
+        <v>2.37</v>
+      </c>
+      <c r="Q4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="R4">
+        <v>2.5884399999999998E-2</v>
+      </c>
+      <c r="S4">
+        <v>0.27560210000000002</v>
+      </c>
+      <c r="T4">
+        <v>0.12570490000000001</v>
+      </c>
+      <c r="U4">
+        <v>3.8006600000000001E-2</v>
+      </c>
+      <c r="V4">
+        <v>3.31</v>
+      </c>
+      <c r="W4">
+        <v>1E-3</v>
+      </c>
+      <c r="X4">
+        <v>5.1199799999999997E-2</v>
+      </c>
+      <c r="Y4">
+        <v>0.20021</v>
+      </c>
+      <c r="Z4">
+        <v>5.1790700000000002E-2</v>
+      </c>
+      <c r="AA4">
+        <v>3.5246899999999998E-2</v>
+      </c>
+      <c r="AB4">
+        <v>1.47</v>
+      </c>
+      <c r="AC4">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>-1.7304300000000002E-2</v>
+      </c>
+      <c r="AE4">
+        <v>0.1208857</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>0.2431431</v>
+      </c>
+      <c r="C5">
+        <v>0.13836809999999999</v>
+      </c>
+      <c r="D5">
+        <v>1.76</v>
+      </c>
+      <c r="E5">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="F5">
+        <v>-2.81023E-2</v>
+      </c>
+      <c r="G5">
+        <v>0.51438839999999997</v>
+      </c>
+      <c r="H5">
+        <v>0.2391269</v>
+      </c>
+      <c r="I5">
+        <v>8.68501E-2</v>
+      </c>
+      <c r="J5">
+        <v>2.75</v>
+      </c>
+      <c r="K5">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="L5">
+        <v>6.8873199999999996E-2</v>
+      </c>
+      <c r="M5">
+        <v>0.40938059999999998</v>
+      </c>
+      <c r="N5">
+        <v>0.29463679999999998</v>
+      </c>
+      <c r="O5">
+        <v>6.2016799999999997E-2</v>
+      </c>
+      <c r="P5">
+        <v>4.75</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0.1730642</v>
+      </c>
+      <c r="S5">
+        <v>0.41620940000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.22456209999999999</v>
+      </c>
+      <c r="U5">
+        <v>4.0112500000000002E-2</v>
+      </c>
+      <c r="V5">
+        <v>5.6</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0.1459289</v>
+      </c>
+      <c r="Y5">
+        <v>0.3031952</v>
+      </c>
+      <c r="Z5">
+        <v>0.10855090000000001</v>
+      </c>
+      <c r="AA5">
+        <v>3.7431199999999998E-2</v>
+      </c>
+      <c r="AB5">
+        <v>2.9</v>
+      </c>
+      <c r="AC5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="AD5">
+        <v>3.5173900000000001E-2</v>
+      </c>
+      <c r="AE5">
+        <v>0.1819279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>0.3056374</v>
+      </c>
+      <c r="C6">
+        <v>0.15490209999999999</v>
+      </c>
+      <c r="D6">
+        <v>1.97</v>
+      </c>
+      <c r="E6">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="F6">
+        <v>1.9802999999999999E-3</v>
+      </c>
+      <c r="G6">
+        <v>0.60929440000000001</v>
+      </c>
+      <c r="H6">
+        <v>0.24472859999999999</v>
+      </c>
+      <c r="I6">
+        <v>9.6229300000000004E-2</v>
+      </c>
+      <c r="J6">
+        <v>2.54</v>
+      </c>
+      <c r="K6">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="L6">
+        <v>5.6088699999999998E-2</v>
+      </c>
+      <c r="M6">
+        <v>0.43336849999999999</v>
+      </c>
+      <c r="N6">
+        <v>0.3745116</v>
+      </c>
+      <c r="O6">
+        <v>6.5215300000000004E-2</v>
+      </c>
+      <c r="P6">
+        <v>5.74</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0.2466689</v>
+      </c>
+      <c r="S6">
+        <v>0.50235430000000003</v>
+      </c>
+      <c r="T6">
+        <v>0.38276749999999998</v>
+      </c>
+      <c r="U6">
+        <v>4.6026999999999998E-2</v>
+      </c>
+      <c r="V6">
+        <v>8.32</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.29254000000000002</v>
+      </c>
+      <c r="Y6">
+        <v>0.4729949</v>
+      </c>
+      <c r="Z6">
+        <v>0.1656726</v>
+      </c>
+      <c r="AA6">
+        <v>4.4182300000000001E-2</v>
+      </c>
+      <c r="AB6">
+        <v>3.75</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>7.9061300000000001E-2</v>
+      </c>
+      <c r="AE6">
+        <v>0.25228390000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>0.4462005</v>
+      </c>
+      <c r="C7">
+        <v>0.16699800000000001</v>
+      </c>
+      <c r="D7">
+        <v>2.67</v>
+      </c>
+      <c r="E7">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F7">
+        <v>0.1188316</v>
+      </c>
+      <c r="G7">
+        <v>0.77356939999999996</v>
+      </c>
+      <c r="H7">
+        <v>0.45693909999999999</v>
+      </c>
+      <c r="I7">
+        <v>0.10295310000000001</v>
+      </c>
+      <c r="J7">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0.25511840000000002</v>
+      </c>
+      <c r="M7">
+        <v>0.65875980000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.53961110000000001</v>
+      </c>
+      <c r="O7">
+        <v>7.4599299999999993E-2</v>
+      </c>
+      <c r="P7">
+        <v>7.23</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0.39337280000000002</v>
+      </c>
+      <c r="S7">
+        <v>0.6858493</v>
+      </c>
+      <c r="T7">
+        <v>0.59362159999999997</v>
+      </c>
+      <c r="U7">
+        <v>5.8016100000000001E-2</v>
+      </c>
+      <c r="V7">
+        <v>10.23</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.47989179999999998</v>
+      </c>
+      <c r="Y7">
+        <v>0.70735150000000002</v>
+      </c>
+      <c r="Z7">
+        <v>0.2508032</v>
+      </c>
+      <c r="AA7">
+        <v>5.8543600000000001E-2</v>
+      </c>
+      <c r="AB7">
+        <v>4.28</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0.1360393</v>
+      </c>
+      <c r="AE7">
+        <v>0.36556709999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>0.69773810000000003</v>
+      </c>
+      <c r="C8">
+        <v>0.16546430000000001</v>
+      </c>
+      <c r="D8">
+        <v>4.22</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.37337559999999997</v>
+      </c>
+      <c r="G8">
+        <v>1.0221</v>
+      </c>
+      <c r="H8">
+        <v>0.69638219999999995</v>
+      </c>
+      <c r="I8">
+        <v>0.10578129999999999</v>
+      </c>
+      <c r="J8">
+        <v>6.58</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0.48901729999999999</v>
+      </c>
+      <c r="M8">
+        <v>0.90374710000000003</v>
+      </c>
+      <c r="N8">
+        <v>0.88513900000000001</v>
+      </c>
+      <c r="O8">
+        <v>7.4984200000000001E-2</v>
+      </c>
+      <c r="P8">
+        <v>11.8</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0.73814610000000003</v>
+      </c>
+      <c r="S8">
+        <v>1.032132</v>
+      </c>
+      <c r="T8">
+        <v>0.91142979999999996</v>
+      </c>
+      <c r="U8">
+        <v>6.2822199999999995E-2</v>
+      </c>
+      <c r="V8">
+        <v>14.51</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.78827840000000005</v>
+      </c>
+      <c r="Y8">
+        <v>1.034581</v>
+      </c>
+      <c r="Z8">
+        <v>0.52909989999999996</v>
+      </c>
+      <c r="AA8">
+        <v>7.9875299999999996E-2</v>
+      </c>
+      <c r="AB8">
+        <v>6.62</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0.37251899999999999</v>
+      </c>
+      <c r="AE8">
+        <v>0.68568070000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>0.70637919999999998</v>
+      </c>
+      <c r="C9">
+        <v>0.15548149999999999</v>
+      </c>
+      <c r="D9">
+        <v>4.54</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0.40158630000000001</v>
+      </c>
+      <c r="G9">
+        <v>1.011172</v>
+      </c>
+      <c r="H9">
+        <v>0.74519899999999994</v>
+      </c>
+      <c r="I9">
+        <v>0.1122891</v>
+      </c>
+      <c r="J9">
+        <v>6.64</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0.52507689999999996</v>
+      </c>
+      <c r="M9">
+        <v>0.96532119999999999</v>
+      </c>
+      <c r="N9">
+        <v>0.96925839999999996</v>
+      </c>
+      <c r="O9">
+        <v>8.7739800000000007E-2</v>
+      </c>
+      <c r="P9">
+        <v>11.05</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0.79726050000000004</v>
+      </c>
+      <c r="S9">
+        <v>1.141256</v>
+      </c>
+      <c r="T9">
+        <v>1.093602</v>
+      </c>
+      <c r="U9">
+        <v>8.0061800000000002E-2</v>
+      </c>
+      <c r="V9">
+        <v>13.66</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0.93665560000000003</v>
+      </c>
+      <c r="Y9">
+        <v>1.2505489999999999</v>
+      </c>
+      <c r="Z9">
+        <v>0.96154660000000003</v>
+      </c>
+      <c r="AA9">
+        <v>0.1094614</v>
+      </c>
+      <c r="AB9">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0.74696759999999995</v>
+      </c>
+      <c r="AE9">
+        <v>1.176126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>-1.20847E-2</v>
+      </c>
+      <c r="C10">
+        <v>1.7269199999999998E-2</v>
+      </c>
+      <c r="D10">
+        <v>-0.7</v>
+      </c>
+      <c r="E10">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="F10">
+        <v>-4.5937899999999997E-2</v>
+      </c>
+      <c r="G10">
+        <v>2.17684E-2</v>
+      </c>
+      <c r="H10" s="2">
+        <v>-6.5709000000000002E-3</v>
+      </c>
+      <c r="I10">
+        <v>1.27606E-2</v>
+      </c>
+      <c r="J10">
+        <v>-0.51</v>
+      </c>
+      <c r="K10">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="L10">
+        <v>-3.1585799999999997E-2</v>
+      </c>
+      <c r="M10">
+        <v>1.8443899999999999E-2</v>
+      </c>
+      <c r="N10">
+        <v>1.8620500000000002E-2</v>
+      </c>
+      <c r="O10">
+        <v>9.7655999999999993E-3</v>
+      </c>
+      <c r="P10">
+        <v>1.91</v>
+      </c>
+      <c r="Q10">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="R10">
+        <v>-5.2320000000000003E-4</v>
+      </c>
+      <c r="S10">
+        <v>3.7764199999999998E-2</v>
+      </c>
+      <c r="T10" s="2">
+        <v>-1.0437999999999999E-3</v>
+      </c>
+      <c r="U10">
+        <v>6.4646E-3</v>
+      </c>
+      <c r="V10">
+        <v>-0.16</v>
+      </c>
+      <c r="W10">
+        <v>0.872</v>
+      </c>
+      <c r="X10">
+        <v>-1.37165E-2</v>
+      </c>
+      <c r="Y10">
+        <v>1.16288E-2</v>
+      </c>
+      <c r="Z10">
+        <v>3.9172E-3</v>
+      </c>
+      <c r="AA10">
+        <v>6.8374999999999998E-3</v>
+      </c>
+      <c r="AB10">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="AC10">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="AD10">
+        <v>-9.4865999999999995E-3</v>
+      </c>
+      <c r="AE10">
+        <v>1.73209E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2">
+        <v>-0.42531649999999999</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.1040875</v>
+      </c>
+      <c r="D11" s="2">
+        <v>-4.09</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>-0.6293609</v>
+      </c>
+      <c r="G11" s="2">
+        <v>-0.2212721</v>
+      </c>
+      <c r="H11" s="2">
+        <v>-0.29161510000000002</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.19228E-2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>-4.71</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>-0.41300330000000002</v>
+      </c>
+      <c r="M11" s="2">
+        <v>-0.17022680000000001</v>
+      </c>
+      <c r="N11" s="2">
+        <v>-0.26786910000000003</v>
+      </c>
+      <c r="O11" s="2">
+        <v>4.3508100000000001E-2</v>
+      </c>
+      <c r="P11" s="2">
+        <v>-6.16</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>-0.35315869999999999</v>
+      </c>
+      <c r="S11" s="2">
+        <v>-0.18257950000000001</v>
+      </c>
+      <c r="T11" s="2">
+        <v>-0.1679252</v>
+      </c>
+      <c r="U11" s="2">
+        <v>3.6826499999999998E-2</v>
+      </c>
+      <c r="V11" s="2">
+        <v>-4.5599999999999996</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>-0.24011689999999999</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>-9.5733600000000002E-2</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>-9.7561200000000001E-2</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>4.0645000000000001E-2</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>-2.4</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>-0.17723820000000001</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>-1.7884199999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2">
+        <v>-4.8004600000000001E-2</v>
+      </c>
+      <c r="C12">
+        <v>9.9481E-2</v>
+      </c>
+      <c r="D12">
+        <v>-0.48</v>
+      </c>
+      <c r="E12">
+        <v>0.629</v>
+      </c>
+      <c r="F12">
+        <v>-0.24301880000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.14700959999999999</v>
+      </c>
+      <c r="H12">
+        <v>6.2892900000000002E-2</v>
+      </c>
+      <c r="I12">
+        <v>7.0318400000000003E-2</v>
+      </c>
+      <c r="J12">
+        <v>0.89</v>
+      </c>
+      <c r="K12">
+        <v>0.371</v>
+      </c>
+      <c r="L12">
+        <v>-7.4953400000000003E-2</v>
+      </c>
+      <c r="M12">
+        <v>0.20073920000000001</v>
+      </c>
+      <c r="N12">
+        <v>0.1295634</v>
+      </c>
+      <c r="O12">
+        <v>4.2872599999999997E-2</v>
+      </c>
+      <c r="P12">
+        <v>3.02</v>
+      </c>
+      <c r="Q12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R12">
+        <v>4.55196E-2</v>
+      </c>
+      <c r="S12">
+        <v>0.2136072</v>
+      </c>
+      <c r="T12" s="2">
+        <v>-1.31936E-2</v>
+      </c>
+      <c r="U12">
+        <v>3.7821300000000002E-2</v>
+      </c>
+      <c r="V12">
+        <v>-0.35</v>
+      </c>
+      <c r="W12">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="X12">
+        <v>-8.7335200000000002E-2</v>
+      </c>
+      <c r="Y12">
+        <v>6.0948099999999998E-2</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>-1.8290399999999998E-2</v>
+      </c>
+      <c r="AA12">
+        <v>4.3806400000000002E-2</v>
+      </c>
+      <c r="AB12">
+        <v>-0.42</v>
+      </c>
+      <c r="AC12">
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="AD12">
+        <v>-0.1041649</v>
+      </c>
+      <c r="AE12">
+        <v>6.7584000000000005E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2">
+        <v>-1.6800699999999998E-2</v>
+      </c>
+      <c r="C13">
+        <v>3.7743400000000003E-2</v>
+      </c>
+      <c r="D13">
+        <v>-0.45</v>
+      </c>
+      <c r="E13">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="F13">
+        <v>-9.0789700000000001E-2</v>
+      </c>
+      <c r="G13">
+        <v>5.7188200000000002E-2</v>
+      </c>
+      <c r="H13">
+        <v>5.2459000000000004E-3</v>
+      </c>
+      <c r="I13">
+        <v>2.5690600000000001E-2</v>
+      </c>
+      <c r="J13">
+        <v>0.2</v>
+      </c>
+      <c r="K13">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="L13">
+        <v>-4.5115700000000002E-2</v>
+      </c>
+      <c r="M13">
+        <v>5.56076E-2</v>
+      </c>
+      <c r="N13" s="2">
+        <v>-5.8830100000000003E-2</v>
+      </c>
+      <c r="O13">
+        <v>1.8754300000000002E-2</v>
+      </c>
+      <c r="P13">
+        <v>-3.14</v>
+      </c>
+      <c r="Q13">
+        <v>2E-3</v>
+      </c>
+      <c r="R13">
+        <v>-9.5594399999999996E-2</v>
+      </c>
+      <c r="S13">
+        <v>-2.2065700000000001E-2</v>
+      </c>
+      <c r="T13" s="2">
+        <v>-2.5487099999999999E-2</v>
+      </c>
+      <c r="U13">
+        <v>1.2722000000000001E-2</v>
+      </c>
+      <c r="V13">
+        <v>-2</v>
+      </c>
+      <c r="W13">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="X13">
+        <v>-5.04263E-2</v>
+      </c>
+      <c r="Y13">
+        <v>-5.4799999999999998E-4</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>-1.9327199999999999E-2</v>
+      </c>
+      <c r="AA13">
+        <v>1.28588E-2</v>
+      </c>
+      <c r="AB13">
+        <v>-1.5</v>
+      </c>
+      <c r="AC13">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>-4.4534499999999998E-2</v>
+      </c>
+      <c r="AE13">
+        <v>5.8799999999999998E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>0.1020915</v>
+      </c>
+      <c r="C14">
+        <v>6.2281900000000001E-2</v>
+      </c>
+      <c r="D14">
+        <v>1.64</v>
+      </c>
+      <c r="E14">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="F14">
+        <v>-2.00007E-2</v>
+      </c>
+      <c r="G14">
+        <v>0.22418360000000001</v>
+      </c>
+      <c r="H14">
+        <v>0.1069918</v>
+      </c>
+      <c r="I14">
+        <v>5.2077100000000001E-2</v>
+      </c>
+      <c r="J14">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K14">
+        <v>0.04</v>
+      </c>
+      <c r="L14">
+        <v>4.9042000000000001E-3</v>
+      </c>
+      <c r="M14">
+        <v>0.2090795</v>
+      </c>
+      <c r="N14">
+        <v>5.2468000000000001E-2</v>
+      </c>
+      <c r="O14">
+        <v>3.9024700000000002E-2</v>
+      </c>
+      <c r="P14">
+        <v>1.34</v>
+      </c>
+      <c r="Q14">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="R14">
+        <v>-2.4032700000000001E-2</v>
+      </c>
+      <c r="S14">
+        <v>0.12896869999999999</v>
+      </c>
+      <c r="T14">
+        <v>4.9824100000000003E-2</v>
+      </c>
+      <c r="U14">
+        <v>3.9921400000000003E-2</v>
+      </c>
+      <c r="V14">
+        <v>1.25</v>
+      </c>
+      <c r="W14">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="X14">
+        <v>-2.8434500000000001E-2</v>
+      </c>
+      <c r="Y14">
+        <v>0.12808259999999999</v>
+      </c>
+      <c r="Z14">
+        <v>7.2508500000000004E-2</v>
+      </c>
+      <c r="AA14">
+        <v>4.5608200000000002E-2</v>
+      </c>
+      <c r="AB14">
+        <v>1.59</v>
+      </c>
+      <c r="AC14">
+        <v>0.112</v>
+      </c>
+      <c r="AD14">
+        <v>-1.6898E-2</v>
+      </c>
+      <c r="AE14">
+        <v>0.161915</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2">
+        <v>-4.24946E-2</v>
+      </c>
+      <c r="C15">
+        <v>0.1061966</v>
+      </c>
+      <c r="D15">
+        <v>-0.4</v>
+      </c>
+      <c r="E15">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="F15">
+        <v>-0.2506737</v>
+      </c>
+      <c r="G15">
+        <v>0.16568440000000001</v>
+      </c>
+      <c r="H15">
+        <v>0.1046631</v>
+      </c>
+      <c r="I15">
+        <v>6.3175700000000001E-2</v>
+      </c>
+      <c r="J15">
+        <v>1.66</v>
+      </c>
+      <c r="K15">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="L15">
+        <v>-1.9181299999999998E-2</v>
+      </c>
+      <c r="M15">
+        <v>0.2285075</v>
+      </c>
+      <c r="N15">
+        <v>0.1619273</v>
+      </c>
+      <c r="O15">
+        <v>4.3352399999999999E-2</v>
+      </c>
+      <c r="P15">
+        <v>3.74</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>7.6942899999999995E-2</v>
+      </c>
+      <c r="S15">
+        <v>0.24691160000000001</v>
+      </c>
+      <c r="T15">
+        <v>0.116728</v>
+      </c>
+      <c r="U15">
+        <v>3.7109499999999997E-2</v>
+      </c>
+      <c r="V15">
+        <v>3.15</v>
+      </c>
+      <c r="W15">
+        <v>2E-3</v>
+      </c>
+      <c r="X15">
+        <v>4.3981600000000003E-2</v>
+      </c>
+      <c r="Y15">
+        <v>0.18947439999999999</v>
+      </c>
+      <c r="Z15">
+        <v>0.1378355</v>
+      </c>
+      <c r="AA15">
+        <v>4.0736899999999999E-2</v>
+      </c>
+      <c r="AB15">
+        <v>3.38</v>
+      </c>
+      <c r="AC15">
+        <v>1E-3</v>
+      </c>
+      <c r="AD15">
+        <v>5.7978200000000001E-2</v>
+      </c>
+      <c r="AE15">
+        <v>0.21769279999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>-4.4683500000000001E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.9456400000000001E-2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>-1.52</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.129</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-0.1024273</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1.30603E-2</v>
+      </c>
+      <c r="H16" s="2">
+        <v>-3.4315900000000003E-2</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1.6571200000000001E-2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>-2.0699999999999998</v>
+      </c>
+      <c r="K16" s="2">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="L16" s="2">
+        <v>-6.6800799999999994E-2</v>
+      </c>
+      <c r="M16" s="2">
+        <v>-1.8311E-3</v>
+      </c>
+      <c r="N16" s="2">
+        <v>-1.8517E-3</v>
+      </c>
+      <c r="O16" s="2">
+        <v>1.1741E-2</v>
+      </c>
+      <c r="P16" s="2">
+        <v>-0.16</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="R16" s="2">
+        <v>-2.48677E-2</v>
+      </c>
+      <c r="S16" s="2">
+        <v>2.11644E-2</v>
+      </c>
+      <c r="T16" s="2">
+        <v>-1.1714499999999999E-2</v>
+      </c>
+      <c r="U16" s="2">
+        <v>1.06248E-2</v>
+      </c>
+      <c r="V16" s="2">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="W16" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="X16" s="2">
+        <v>-3.2542399999999999E-2</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>9.1134000000000007E-3</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>-1.63295E-2</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>1.0728100000000001E-2</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>-1.52</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0.128</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>-3.7359999999999997E-2</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>4.7010999999999997E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>0.11203680000000001</v>
+      </c>
+      <c r="C17">
+        <v>5.8797299999999997E-2</v>
+      </c>
+      <c r="D17">
+        <v>1.91</v>
+      </c>
+      <c r="E17">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="F17">
+        <v>-3.2246000000000002E-3</v>
+      </c>
+      <c r="G17">
+        <v>0.22729820000000001</v>
+      </c>
+      <c r="H17">
+        <v>0.18790870000000001</v>
+      </c>
+      <c r="I17">
+        <v>5.1274899999999998E-2</v>
+      </c>
+      <c r="J17">
+        <v>3.66</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>8.7393799999999994E-2</v>
+      </c>
+      <c r="M17">
+        <v>0.28842370000000001</v>
+      </c>
+      <c r="N17">
+        <v>4.9411799999999999E-2</v>
+      </c>
+      <c r="O17">
+        <v>3.5296300000000003E-2</v>
+      </c>
+      <c r="P17">
+        <v>1.4</v>
+      </c>
+      <c r="Q17">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="R17">
+        <v>-1.9780099999999998E-2</v>
+      </c>
+      <c r="S17">
+        <v>0.1186038</v>
+      </c>
+      <c r="T17">
+        <v>-1.1276899999999999E-2</v>
+      </c>
+      <c r="U17">
+        <v>2.8718400000000002E-2</v>
+      </c>
+      <c r="V17">
+        <v>-0.39</v>
+      </c>
+      <c r="W17">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="X17">
+        <v>-6.7574099999999998E-2</v>
+      </c>
+      <c r="Y17">
+        <v>4.5020400000000002E-2</v>
+      </c>
+      <c r="Z17">
+        <v>-2.4942099999999998E-2</v>
+      </c>
+      <c r="AA17">
+        <v>3.6178299999999997E-2</v>
+      </c>
+      <c r="AB17">
+        <v>-0.69</v>
+      </c>
+      <c r="AC17">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AD17">
+        <v>-9.5863000000000004E-2</v>
+      </c>
+      <c r="AE17">
+        <v>4.5978699999999997E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2">
+        <v>-0.1035185</v>
+      </c>
+      <c r="C18" s="2">
+        <v>5.5514599999999997E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>-1.86</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6.2E-2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-0.21234459999999999</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5.3076E-3</v>
+      </c>
+      <c r="H18" s="2">
+        <v>-0.16936909999999999</v>
+      </c>
+      <c r="I18" s="2">
+        <v>4.2751299999999999E-2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>-3.96</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>-0.25317519999999999</v>
+      </c>
+      <c r="M18" s="2">
+        <v>-8.5563E-2</v>
+      </c>
+      <c r="N18" s="2">
+        <v>-0.29362700000000003</v>
+      </c>
+      <c r="O18" s="2">
+        <v>3.79631E-2</v>
+      </c>
+      <c r="P18" s="2">
+        <v>-7.73</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="2">
+        <v>-0.36804680000000001</v>
+      </c>
+      <c r="S18" s="2">
+        <v>-0.21920719999999999</v>
+      </c>
+      <c r="T18" s="2">
+        <v>-0.28428049999999999</v>
+      </c>
+      <c r="U18" s="2">
+        <v>3.7038799999999997E-2</v>
+      </c>
+      <c r="V18" s="2">
+        <v>-7.68</v>
+      </c>
+      <c r="W18" s="2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="2">
+        <v>-0.35688829999999999</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>-0.21167259999999999</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>-0.21457290000000001</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>3.8837999999999998E-2</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>-5.52</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>-0.29070770000000001</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>-0.13843810000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>0.41640129999999997</v>
+      </c>
+      <c r="C19">
+        <v>0.32075749999999997</v>
+      </c>
+      <c r="D19">
+        <v>1.3</v>
+      </c>
+      <c r="E19">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="F19">
+        <v>-0.21238499999999999</v>
+      </c>
+      <c r="G19">
+        <v>1.0451870000000001</v>
+      </c>
+      <c r="H19">
+        <v>0.24458360000000001</v>
+      </c>
+      <c r="I19">
+        <v>0.15333479999999999</v>
+      </c>
+      <c r="J19">
+        <v>1.6</v>
+      </c>
+      <c r="K19">
+        <v>0.111</v>
+      </c>
+      <c r="L19">
+        <v>-5.6001099999999998E-2</v>
+      </c>
+      <c r="M19">
+        <v>0.54516830000000005</v>
+      </c>
+      <c r="N19">
+        <v>0.15029020000000001</v>
+      </c>
+      <c r="O19">
+        <v>9.9704399999999999E-2</v>
+      </c>
+      <c r="P19">
+        <v>1.51</v>
+      </c>
+      <c r="Q19">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="R19">
+        <v>-4.5162000000000001E-2</v>
+      </c>
+      <c r="S19">
+        <v>0.3457423</v>
+      </c>
+      <c r="T19">
+        <v>-1.3570799999999999E-2</v>
+      </c>
+      <c r="U19">
+        <v>0.1049213</v>
+      </c>
+      <c r="V19">
+        <v>-0.13</v>
+      </c>
+      <c r="W19">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="X19">
+        <v>-0.21924969999999999</v>
+      </c>
+      <c r="Y19">
+        <v>0.1921081</v>
+      </c>
+      <c r="Z19">
+        <v>-1.3474099999999999E-2</v>
+      </c>
+      <c r="AA19">
+        <v>8.7157200000000004E-2</v>
+      </c>
+      <c r="AB19">
+        <v>-0.15</v>
+      </c>
+      <c r="AC19">
+        <v>0.877</v>
+      </c>
+      <c r="AD19">
+        <v>-0.18432970000000001</v>
+      </c>
+      <c r="AE19">
+        <v>0.15738160000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>0.6809849</v>
+      </c>
+      <c r="C20">
+        <v>0.31934630000000003</v>
+      </c>
+      <c r="D20">
+        <v>2.13</v>
+      </c>
+      <c r="E20">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="F20">
+        <v>5.4965100000000003E-2</v>
+      </c>
+      <c r="G20">
+        <v>1.307005</v>
+      </c>
+      <c r="H20">
+        <v>0.52804419999999996</v>
+      </c>
+      <c r="I20">
+        <v>0.13212289999999999</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0.26904149999999999</v>
+      </c>
+      <c r="M20">
+        <v>0.78704700000000005</v>
+      </c>
+      <c r="N20">
+        <v>0.44524259999999999</v>
+      </c>
+      <c r="O20">
+        <v>7.9124100000000003E-2</v>
+      </c>
+      <c r="P20">
+        <v>5.63</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0.29013440000000001</v>
+      </c>
+      <c r="S20">
+        <v>0.60035079999999996</v>
+      </c>
+      <c r="T20">
+        <v>4.8184400000000002E-2</v>
+      </c>
+      <c r="U20">
+        <v>9.0363200000000005E-2</v>
+      </c>
+      <c r="V20">
+        <v>0.53</v>
+      </c>
+      <c r="W20">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="X20">
+        <v>-0.12895609999999999</v>
+      </c>
+      <c r="Y20">
+        <v>0.22532489999999999</v>
+      </c>
+      <c r="Z20">
+        <v>2.92194E-2</v>
+      </c>
+      <c r="AA20">
+        <v>7.3450000000000001E-2</v>
+      </c>
+      <c r="AB20">
+        <v>0.4</v>
+      </c>
+      <c r="AC20">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="AD20">
+        <v>-0.1147658</v>
+      </c>
+      <c r="AE20">
+        <v>0.17320450000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>0.4089024</v>
+      </c>
+      <c r="C21">
+        <v>0.32853719999999997</v>
+      </c>
+      <c r="D21">
+        <v>1.24</v>
+      </c>
+      <c r="E21">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="F21">
+        <v>-0.2351346</v>
+      </c>
+      <c r="G21">
+        <v>1.0529390000000001</v>
+      </c>
+      <c r="H21">
+        <v>0.23656179999999999</v>
+      </c>
+      <c r="I21">
+        <v>0.14353279999999999</v>
+      </c>
+      <c r="J21">
+        <v>1.65</v>
+      </c>
+      <c r="K21">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="L21">
+        <v>-4.4807800000000002E-2</v>
+      </c>
+      <c r="M21">
+        <v>0.51793149999999999</v>
+      </c>
+      <c r="N21">
+        <v>9.2650899999999994E-2</v>
+      </c>
+      <c r="O21">
+        <v>8.6898799999999998E-2</v>
+      </c>
+      <c r="P21">
+        <v>1.07</v>
+      </c>
+      <c r="Q21">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="R21">
+        <v>-7.7698199999999995E-2</v>
+      </c>
+      <c r="S21">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="T21" s="2">
+        <v>-2.3532299999999999E-2</v>
+      </c>
+      <c r="U21">
+        <v>9.1362700000000005E-2</v>
+      </c>
+      <c r="V21">
+        <v>-0.26</v>
+      </c>
+      <c r="W21">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="X21">
+        <v>-0.20263210000000001</v>
+      </c>
+      <c r="Y21">
+        <v>0.1555675</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>-2.97387E-2</v>
+      </c>
+      <c r="AA21">
+        <v>7.0834599999999998E-2</v>
+      </c>
+      <c r="AB21">
+        <v>-0.42</v>
+      </c>
+      <c r="AC21">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="AD21">
+        <v>-0.1685971</v>
+      </c>
+      <c r="AE21">
+        <v>0.1091196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>0.14883389999999999</v>
+      </c>
+      <c r="C22">
+        <v>0.33171040000000002</v>
+      </c>
+      <c r="D22">
+        <v>0.45</v>
+      </c>
+      <c r="E22">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="F22">
+        <v>-0.50142350000000002</v>
+      </c>
+      <c r="G22">
+        <v>0.7990912</v>
+      </c>
+      <c r="H22">
+        <v>0.13261899999999999</v>
+      </c>
+      <c r="I22">
+        <v>0.1390015</v>
+      </c>
+      <c r="J22">
+        <v>0.95</v>
+      </c>
+      <c r="K22">
+        <v>0.34</v>
+      </c>
+      <c r="L22">
+        <v>-0.13986779999999999</v>
+      </c>
+      <c r="M22">
+        <v>0.40510590000000002</v>
+      </c>
+      <c r="N22">
+        <v>0.12796640000000001</v>
+      </c>
+      <c r="O22">
+        <v>8.1249500000000002E-2</v>
+      </c>
+      <c r="P22">
+        <v>1.57</v>
+      </c>
+      <c r="Q22">
+        <v>0.115</v>
+      </c>
+      <c r="R22">
+        <v>-3.1308299999999997E-2</v>
+      </c>
+      <c r="S22">
+        <v>0.28724110000000003</v>
+      </c>
+      <c r="T22">
+        <v>8.9160000000000003E-3</v>
+      </c>
+      <c r="U22">
+        <v>8.91015E-2</v>
+      </c>
+      <c r="V22">
+        <v>0.1</v>
+      </c>
+      <c r="W22">
+        <v>0.92</v>
+      </c>
+      <c r="X22">
+        <v>-0.16575119999999999</v>
+      </c>
+      <c r="Y22">
+        <v>0.1835831</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>-1.3351999999999999E-3</v>
+      </c>
+      <c r="AA22">
+        <v>6.9434399999999993E-2</v>
+      </c>
+      <c r="AB22">
+        <v>-0.02</v>
+      </c>
+      <c r="AC22">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="AD22">
+        <v>-0.1374486</v>
+      </c>
+      <c r="AE22">
+        <v>0.13477819999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>0.35032639999999998</v>
+      </c>
+      <c r="C23">
+        <v>0.31750139999999999</v>
+      </c>
+      <c r="D23">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E23">
+        <v>0.27</v>
+      </c>
+      <c r="F23">
+        <v>-0.2720767</v>
+      </c>
+      <c r="G23">
+        <v>0.97272959999999997</v>
+      </c>
+      <c r="H23">
+        <v>0.25757750000000001</v>
+      </c>
+      <c r="I23">
+        <v>0.13888700000000001</v>
+      </c>
+      <c r="J23">
+        <v>1.85</v>
+      </c>
+      <c r="K23">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="L23">
+        <v>-1.4685E-2</v>
+      </c>
+      <c r="M23">
+        <v>0.52983990000000003</v>
+      </c>
+      <c r="N23">
+        <v>0.20858460000000001</v>
+      </c>
+      <c r="O23">
+        <v>8.2376900000000003E-2</v>
+      </c>
+      <c r="P23">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="Q23">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R23">
+        <v>4.70999E-2</v>
+      </c>
+      <c r="S23">
+        <v>0.37006939999999999</v>
+      </c>
+      <c r="T23">
+        <v>7.9535900000000007E-2</v>
+      </c>
+      <c r="U23">
+        <v>8.8669100000000001E-2</v>
+      </c>
+      <c r="V23">
+        <v>0.9</v>
+      </c>
+      <c r="W23">
+        <v>0.37</v>
+      </c>
+      <c r="X23">
+        <v>-9.4283500000000006E-2</v>
+      </c>
+      <c r="Y23">
+        <v>0.25335530000000001</v>
+      </c>
+      <c r="Z23">
+        <v>3.2817399999999997E-2</v>
+      </c>
+      <c r="AA23">
+        <v>7.4366500000000002E-2</v>
+      </c>
+      <c r="AB23">
+        <v>0.44</v>
+      </c>
+      <c r="AC23">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="AD23">
+        <v>-0.11296440000000001</v>
+      </c>
+      <c r="AE23">
+        <v>0.17859920000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>3.0869710000000001</v>
+      </c>
+      <c r="C24">
+        <v>0.33289459999999998</v>
+      </c>
+      <c r="D24">
+        <v>9.27</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>2.434393</v>
+      </c>
+      <c r="G24">
+        <v>3.7395499999999999</v>
+      </c>
+      <c r="H24">
+        <v>3.21238</v>
+      </c>
+      <c r="I24">
+        <v>0.17505399999999999</v>
+      </c>
+      <c r="J24">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>2.8692190000000002</v>
+      </c>
+      <c r="M24">
+        <v>3.5555409999999998</v>
+      </c>
+      <c r="N24">
+        <v>3.5963530000000001</v>
+      </c>
+      <c r="O24">
+        <v>0.1166039</v>
+      </c>
+      <c r="P24">
+        <v>30.84</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>3.3677730000000001</v>
+      </c>
+      <c r="S24">
+        <v>3.8249339999999998</v>
+      </c>
+      <c r="T24">
+        <v>4.2212240000000003</v>
+      </c>
+      <c r="U24">
+        <v>0.1174748</v>
+      </c>
+      <c r="V24">
+        <v>35.93</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>3.990936</v>
+      </c>
+      <c r="Y24">
+        <v>4.4515120000000001</v>
+      </c>
+      <c r="Z24">
+        <v>4.7333179999999997</v>
+      </c>
+      <c r="AA24">
+        <v>0.1003242</v>
+      </c>
+      <c r="AB24">
+        <v>47.18</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>4.536651</v>
+      </c>
+      <c r="AE24">
+        <v>4.9299850000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>